--- a/Storage/SampleData/Card.xlsx
+++ b/Storage/SampleData/Card.xlsx
@@ -1,26 +1,391 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27CC0AB-4352-4909-A946-A6F80DD43E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-16305" yWindow="13335" windowWidth="16410" windowHeight="9975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Card" sheetId="1" r:id="rId1"/>
+    <sheet name="CardUnit" sheetId="5" r:id="rId2"/>
+    <sheet name="UnitStartUp" sheetId="4" r:id="rId3"/>
+    <sheet name="CardSkill" sheetId="8" r:id="rId4"/>
+    <sheet name="CardEffect" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int32</t>
+  </si>
+  <si>
+    <t>int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string(64)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_deck_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파이어볼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pirze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin_res</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>String(128)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m1_tmp/card_img/u_slime.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset/m1_tmp/card_img/s_fire_ball.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arts_cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arts_condition_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_condition_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardCondition</t>
+  </si>
+  <si>
+    <t>card_condition_value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_condition_value2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Unit - CardUnit 테이블
+2.Skill - CardSkill 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 카드 등장 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아츠 사용 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 카드 등장 직전 효과
+(ex 릴리스 소재)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on_play_condition_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등장 이후 효과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on_play_condition_value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on_play_condition_value2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>before_play_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>on_play_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arts_condition_vaule1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arts_condition_vaule2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아츠 사용 직후 효과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>after_arts_effect_id2</t>
+  </si>
+  <si>
+    <t>before_arts_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아츠 사용 직전 효과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_start_up_id1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_start_up_id2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 기동 효과 1번 외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 기동 효과 2번 외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_passive_id1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unit_passive_id2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 패시브 1번 외래키
+(미구현)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유닛 패시브 2번 외래키
+(미구현)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_count_per_turn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>턴당 발동 가능 횟수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더미데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyUnitExist</t>
+  </si>
+  <si>
+    <t>기동 효과 사용 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_cost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스칼 카드 사용 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 카드 사용 직전 효과
+(ex 릴리스 소재)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 이후 효과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_condition_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_condition_value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_condition_value2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_play_effect_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_function_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_function_value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_function_value2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectFunctionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_target_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OppentUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pow 300 이하 적 1장 파괴(승점 x)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_target_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_target_condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectTargetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectTargetCondition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PowerUnderOrEqual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_target_condition_value1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect_target_condition_value2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KillUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +393,74 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAD4FE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +468,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFAD4FE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -66,6 +531,101 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}" name="Card" displayName="Card" ref="A2:E5" totalsRowShown="0">
+  <autoFilter ref="A2:E5" xr:uid="{8A3D1B8D-4816-4AE6-A295-2D1EB19F9C34}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AA48A7AE-3BB5-4D28-B310-C246BE1D73A9}" name="id"/>
+    <tableColumn id="2" xr3:uid="{736DFCAA-9BE9-4E13-AC78-9D961C82FC72}" name="name"/>
+    <tableColumn id="3" xr3:uid="{3F1A7E20-AE75-4F56-AF77-A6731B423C22}" name="type"/>
+    <tableColumn id="4" xr3:uid="{09C7054B-E207-4417-8912-05F77F03E55C}" name="max_deck_count"/>
+    <tableColumn id="5" xr3:uid="{FE50EA62-F0B3-4EEC-969B-204ABADBD546}" name="skin_res"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}" name="CardUnit" displayName="CardUnit" ref="A2:S4" totalsRowShown="0">
+  <autoFilter ref="A2:S4" xr:uid="{10D18713-5237-49EF-95C5-35DA8E23CF32}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{E1C732DB-5275-4BF3-8215-44D4B7F98F34}" name="id"/>
+    <tableColumn id="2" xr3:uid="{AA754E55-C3C2-4F3C-A9D2-8AE9F68682DC}" name="#desc"/>
+    <tableColumn id="3" xr3:uid="{7032B4B8-4205-47FC-9689-BC42E6DF9D37}" name="pirze"/>
+    <tableColumn id="28" xr3:uid="{29A4D6B9-AB36-40F4-B8A4-C9B6870FC42E}" name="arts_cost"/>
+    <tableColumn id="27" xr3:uid="{A9A2C876-6B0F-4AFE-A5DA-1F3B17D95FB6}" name="power"/>
+    <tableColumn id="19" xr3:uid="{3E5C884A-7EF6-4486-A1A0-D6FED59BF178}" name="on_play_condition_type"/>
+    <tableColumn id="20" xr3:uid="{F7DC9C28-B2FA-4A46-8C80-E1718BB22F79}" name="on_play_condition_value1"/>
+    <tableColumn id="21" xr3:uid="{4E5F462A-B93A-4582-B6D7-603E6CD1D818}" name="on_play_condition_value2"/>
+    <tableColumn id="25" xr3:uid="{A459D870-AEF6-42F8-B99F-B2BE68769384}" name="before_play_effect_id"/>
+    <tableColumn id="30" xr3:uid="{DE7482C3-C539-464A-9E32-6BB43781E981}" name="on_play_effect_id"/>
+    <tableColumn id="32" xr3:uid="{6A4EEC22-E9FA-4E76-BAC6-EF142FE312DF}" name="arts_condition_type"/>
+    <tableColumn id="33" xr3:uid="{5911D336-1F67-4FCC-9F5D-6F170FE4163D}" name="arts_condition_vaule1"/>
+    <tableColumn id="34" xr3:uid="{AAFC2702-D99E-4FCA-B62E-06BEDDE4A348}" name="arts_condition_vaule2"/>
+    <tableColumn id="36" xr3:uid="{1BB51C8F-A1E5-43EE-8DBB-33DD7E89CBB0}" name="before_arts_effect_id"/>
+    <tableColumn id="35" xr3:uid="{7B5B7FE9-F4FD-4F2B-B7CB-706949EAAA6A}" name="after_arts_effect_id2"/>
+    <tableColumn id="39" xr3:uid="{99DEE245-8357-4369-93DC-933C127809F3}" name="unit_passive_id1"/>
+    <tableColumn id="40" xr3:uid="{6F79C352-FDFC-420F-8242-ED954F95CAA9}" name="unit_passive_id2"/>
+    <tableColumn id="10" xr3:uid="{2B97404B-E8EB-4E85-9C4E-CFCF5D725C33}" name="unit_start_up_id1"/>
+    <tableColumn id="11" xr3:uid="{E924433F-E951-4720-83F2-5B27EC07B4C3}" name="unit_start_up_id2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}" name="UnitStartUp" displayName="UnitStartUp" ref="A2:G4" totalsRowShown="0">
+  <autoFilter ref="A2:G4" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{AAEBA0B0-7565-4B13-B9C8-A4A5F0860F43}" name="id"/>
+    <tableColumn id="2" xr3:uid="{97590F1E-75D6-4CE3-A145-DD2939DDB4CA}" name="#desc"/>
+    <tableColumn id="3" xr3:uid="{38287567-1E25-443D-BC28-215FFAA01862}" name="use_count_per_turn"/>
+    <tableColumn id="4" xr3:uid="{F1C6AF9B-CC4F-4176-9832-5049338F1646}" name="card_condition_type"/>
+    <tableColumn id="5" xr3:uid="{ACD7DAA8-ADC5-40E6-8B16-A451214C5B84}" name="card_condition_value1"/>
+    <tableColumn id="6" xr3:uid="{566E7172-0BB2-49AD-BEE7-4519B8ED7880}" name="card_condition_value2"/>
+    <tableColumn id="7" xr3:uid="{8C04C062-0B72-4FEE-96D4-BF8765EA018E}" name="card_effect_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}" name="CardSkill" displayName="CardSkill" ref="A2:H4" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="A2:H4" xr:uid="{0273B5A0-2096-4E98-9DA5-9EF706D4F125}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{8D4780BB-DB0E-4DB7-98EE-B9656815F7E3}" name="id"/>
+    <tableColumn id="2" xr3:uid="{930486ED-C78F-4EB0-A0FF-6750226B4381}" name="#desc"/>
+    <tableColumn id="3" xr3:uid="{E1E06BC9-C21F-44D1-AEEB-BA85426B8332}" name="skill_cost"/>
+    <tableColumn id="4" xr3:uid="{B1591891-D015-470D-84EF-F5BCE8D0B39A}" name="use_condition_type"/>
+    <tableColumn id="5" xr3:uid="{679497A7-A7A1-4666-85D3-098B0B4B862D}" name="use_condition_value1"/>
+    <tableColumn id="6" xr3:uid="{57B82F79-74DE-4875-BCDC-DEF43858E6A9}" name="use_condition_value2"/>
+    <tableColumn id="7" xr3:uid="{04160E34-BAA6-4F91-AE2C-A00329E42C34}" name="use_play_effect_id"/>
+    <tableColumn id="8" xr3:uid="{D224225B-4E64-4356-A1B4-49989904FB92}" name="use_effect_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}" name="CardEffect" displayName="CardEffect" ref="A2:K4" totalsRowShown="0">
+  <autoFilter ref="A2:K4" xr:uid="{0506C9DB-265A-41ED-AD27-695A6A11D642}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{293ED03F-3ECA-45BE-AFB4-C19E49058BDA}" name="id"/>
+    <tableColumn id="2" xr3:uid="{301FB54A-AD16-4587-A00B-B96F748C89A7}" name="#group"/>
+    <tableColumn id="3" xr3:uid="{75C34BC9-54EC-46BB-AF94-4EBAFEE39E71}" name="#desc"/>
+    <tableColumn id="4" xr3:uid="{3B827395-6EE4-4784-881F-099E1A02D785}" name="effect_target_type"/>
+    <tableColumn id="5" xr3:uid="{AE86E6C6-7D2B-403C-89ED-1B9327E3BDE3}" name="effect_target_value"/>
+    <tableColumn id="6" xr3:uid="{4C21BEAD-C607-467B-81E3-E382956E2A5C}" name="effect_target_condition"/>
+    <tableColumn id="7" xr3:uid="{CAF0F5B9-A20A-4C26-B38A-999AA80CB8C1}" name="effect_target_condition_value1"/>
+    <tableColumn id="8" xr3:uid="{E0F663F5-43E0-4987-84C7-41024629F4E1}" name="effect_target_condition_value2"/>
+    <tableColumn id="9" xr3:uid="{80FE3837-7081-4542-BC38-4C4B329E81B4}" name="effect_function_type"/>
+    <tableColumn id="10" xr3:uid="{17ABB526-54EF-425A-86C2-EC87E65A11A8}" name="effect_function_value1"/>
+    <tableColumn id="11" xr3:uid="{C98FB8C1-8CFD-448B-A187-F4677EE89B1A}" name="effect_function_value2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +890,669 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+      <c r="C1" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>11001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>21001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94E6BAE-6D4F-4269-A5A9-7C25ADDEB0D7}">
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="25.5" customWidth="1"/>
+    <col min="18" max="18" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="11.625" customWidth="1"/>
+    <col min="23" max="23" width="13.5" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="33" x14ac:dyDescent="0.3">
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>11001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>300</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
+        <v>-1</v>
+      </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4">
+        <v>-1</v>
+      </c>
+      <c r="M4">
+        <v>-1</v>
+      </c>
+      <c r="N4">
+        <v>-1</v>
+      </c>
+      <c r="O4">
+        <v>-1</v>
+      </c>
+      <c r="P4">
+        <v>-1</v>
+      </c>
+      <c r="Q4">
+        <v>-1</v>
+      </c>
+      <c r="R4">
+        <v>-1</v>
+      </c>
+      <c r="S4">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64D7676-E8C5-4ED3-9B18-1BAFD4D2AEAC}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>9999</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>9999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D387B383-5476-4EAA-BAC3-1341BA705F84}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
+    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="D1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>21001</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>-1</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+      <c r="H4">
+        <v>210011</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9DDD54-1F13-4B9B-9D90-4E3358700141}">
+  <dimension ref="A2:K4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="3" max="3" width="28.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.375" customWidth="1"/>
+    <col min="6" max="6" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="29.5" customWidth="1"/>
+    <col min="9" max="9" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>210011</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4">
+        <v>300</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Storage/SampleData/Card.xlsx
+++ b/Storage/SampleData/Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27CC0AB-4352-4909-A946-A6F80DD43E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60484CF2-DFA4-400F-BF5A-656CD7BF8855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16305" yWindow="13335" windowWidth="16410" windowHeight="9975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,6 +378,18 @@
   </si>
   <si>
     <t>KillUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string(128)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드의 스킬 설명 텍스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,7 +498,7 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -576,12 +588,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}" name="UnitStartUp" displayName="UnitStartUp" ref="A2:G4" totalsRowShown="0">
-  <autoFilter ref="A2:G4" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}" name="UnitStartUp" displayName="UnitStartUp" ref="A2:H4" totalsRowShown="0">
+  <autoFilter ref="A2:H4" xr:uid="{B66E93FB-1FE9-4AD8-8283-FD51DC9EF62A}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{AAEBA0B0-7565-4B13-B9C8-A4A5F0860F43}" name="id"/>
     <tableColumn id="2" xr3:uid="{97590F1E-75D6-4CE3-A145-DD2939DDB4CA}" name="#desc"/>
     <tableColumn id="3" xr3:uid="{38287567-1E25-443D-BC28-215FFAA01862}" name="use_count_per_turn"/>
+    <tableColumn id="8" xr3:uid="{77EAFF1F-30F5-4777-92D2-FA0A03D23134}" name="desc"/>
     <tableColumn id="4" xr3:uid="{F1C6AF9B-CC4F-4176-9832-5049338F1646}" name="card_condition_type"/>
     <tableColumn id="5" xr3:uid="{ACD7DAA8-ADC5-40E6-8B16-A451214C5B84}" name="card_condition_value1"/>
     <tableColumn id="6" xr3:uid="{566E7172-0BB2-49AD-BEE7-4519B8ED7880}" name="card_condition_value2"/>
@@ -1228,25 +1241,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64D7676-E8C5-4ED3-9B18-1BAFD4D2AEAC}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
-    <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="3" max="4" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="6" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1257,19 +1270,22 @@
         <v>55</v>
       </c>
       <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1278,19 +1294,22 @@
         <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>9999</v>
       </c>
@@ -1301,15 +1320,18 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>9999</v>
       </c>
     </row>
